--- a/metas.xlsx
+++ b/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/04 Abril/Liquidacióncvs - ensayo/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="797" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72A18988-6FB0-453F-95D0-170F45B19DAE}"/>
+  <xr:revisionPtr revIDLastSave="864" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4003AA5-ABF3-4BE0-A9DF-AD5AF78E01DC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -618,7 +618,7 @@
         <v>29</v>
       </c>
       <c r="D5" s="2">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="E5" s="2">
         <v>2800</v>
@@ -788,7 +788,7 @@
         <v>29</v>
       </c>
       <c r="D15" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E15" s="2">
         <v>1350</v>
@@ -805,7 +805,7 @@
         <v>30</v>
       </c>
       <c r="D16" s="2">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2">
         <v>1350</v>
@@ -825,7 +825,7 @@
         <v>800</v>
       </c>
       <c r="E17" s="2">
-        <v>1700</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -873,7 +873,7 @@
         <v>29</v>
       </c>
       <c r="D20" s="2">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2">
         <v>1500</v>
@@ -890,7 +890,7 @@
         <v>30</v>
       </c>
       <c r="D21" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="E21" s="2">
         <v>1500</v>
@@ -958,7 +958,7 @@
         <v>29</v>
       </c>
       <c r="D25" s="2">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="E25" s="2">
         <v>1450</v>
@@ -975,7 +975,7 @@
         <v>30</v>
       </c>
       <c r="D26" s="2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E26" s="2">
         <v>1450</v>
@@ -1043,7 +1043,7 @@
         <v>29</v>
       </c>
       <c r="D30" s="2">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E30" s="2">
         <v>1500</v>
@@ -1060,7 +1060,7 @@
         <v>30</v>
       </c>
       <c r="D31" s="2">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="E31" s="2">
         <v>1500</v>
@@ -1128,7 +1128,7 @@
         <v>29</v>
       </c>
       <c r="D35" s="2">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="E35" s="2">
         <v>4000</v>
@@ -1145,7 +1145,7 @@
         <v>30</v>
       </c>
       <c r="D36" s="2">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="E36" s="2">
         <v>4000</v>
@@ -1165,7 +1165,7 @@
         <v>1500</v>
       </c>
       <c r="E37" s="2">
-        <v>2600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1213,7 +1213,7 @@
         <v>29</v>
       </c>
       <c r="D40" s="2">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="E40" s="2">
         <v>2400</v>
@@ -1230,7 +1230,7 @@
         <v>30</v>
       </c>
       <c r="D41" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E41" s="2">
         <v>2400</v>
@@ -1298,7 +1298,7 @@
         <v>29</v>
       </c>
       <c r="D45" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E45" s="2">
         <v>2000</v>
@@ -1315,7 +1315,7 @@
         <v>30</v>
       </c>
       <c r="D46" s="2">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="E46" s="2">
         <v>2000</v>
@@ -1383,7 +1383,7 @@
         <v>29</v>
       </c>
       <c r="D50" s="2">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="E50" s="2">
         <v>1500</v>
@@ -1400,7 +1400,7 @@
         <v>30</v>
       </c>
       <c r="D51" s="2">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="E51" s="2">
         <v>1500</v>
@@ -1468,7 +1468,7 @@
         <v>29</v>
       </c>
       <c r="D55" s="2">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="E55" s="2">
         <v>2000</v>
@@ -1485,7 +1485,7 @@
         <v>30</v>
       </c>
       <c r="D56" s="2">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="E56" s="2">
         <v>2000</v>
@@ -1553,7 +1553,7 @@
         <v>29</v>
       </c>
       <c r="D60" s="2">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="E60" s="2">
         <v>1100</v>
@@ -1570,7 +1570,7 @@
         <v>30</v>
       </c>
       <c r="D61" s="2">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="E61" s="2">
         <v>1100</v>
@@ -1638,7 +1638,7 @@
         <v>29</v>
       </c>
       <c r="D65" s="2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E65" s="2">
         <v>2200</v>
@@ -1655,7 +1655,7 @@
         <v>30</v>
       </c>
       <c r="D66" s="2">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E66" s="2">
         <v>2200</v>
@@ -1723,7 +1723,7 @@
         <v>29</v>
       </c>
       <c r="D70" s="2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E70" s="2">
         <v>1600</v>
@@ -1740,7 +1740,7 @@
         <v>30</v>
       </c>
       <c r="D71" s="2">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="E71" s="2">
         <v>1600</v>
@@ -1808,7 +1808,7 @@
         <v>29</v>
       </c>
       <c r="D75" s="2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E75" s="2">
         <v>2200</v>
@@ -1825,7 +1825,7 @@
         <v>30</v>
       </c>
       <c r="D76" s="2">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E76" s="2">
         <v>2200</v>
@@ -1893,7 +1893,7 @@
         <v>29</v>
       </c>
       <c r="D80" s="2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E80" s="2">
         <v>2850</v>
@@ -1910,7 +1910,7 @@
         <v>30</v>
       </c>
       <c r="D81" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="E81" s="2">
         <v>2850</v>
@@ -1978,7 +1978,7 @@
         <v>29</v>
       </c>
       <c r="D85" s="2">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="E85" s="2">
         <v>3500</v>
@@ -1995,7 +1995,7 @@
         <v>30</v>
       </c>
       <c r="D86" s="2">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="E86" s="2">
         <v>3500</v>
@@ -2063,7 +2063,7 @@
         <v>29</v>
       </c>
       <c r="D90" s="2">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E90" s="2">
         <v>3500</v>
@@ -2080,7 +2080,7 @@
         <v>30</v>
       </c>
       <c r="D91" s="2">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="E91" s="2">
         <v>3500</v>
@@ -2148,7 +2148,7 @@
         <v>29</v>
       </c>
       <c r="D95" s="2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E95" s="2">
         <v>2300</v>
@@ -2233,7 +2233,7 @@
         <v>29</v>
       </c>
       <c r="D100" s="2">
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="E100" s="2">
         <v>6000</v>
@@ -2250,7 +2250,7 @@
         <v>30</v>
       </c>
       <c r="D101" s="2">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="E101" s="2">
         <v>6000</v>
@@ -2318,7 +2318,7 @@
         <v>29</v>
       </c>
       <c r="D105" s="2">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="E105" s="2">
         <v>2600</v>
@@ -2335,7 +2335,7 @@
         <v>30</v>
       </c>
       <c r="D106" s="2">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="E106" s="2">
         <v>2600</v>
@@ -2403,7 +2403,7 @@
         <v>29</v>
       </c>
       <c r="D110" s="2">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="E110" s="2">
         <v>2650</v>
@@ -2420,7 +2420,7 @@
         <v>30</v>
       </c>
       <c r="D111" s="2">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="E111" s="2">
         <v>2650</v>
@@ -2453,7 +2453,7 @@
       <c r="C113" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="2">
         <v>820</v>
       </c>
       <c r="E113" s="2">
@@ -2538,7 +2538,7 @@
       <c r="C118" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="2">
         <v>820</v>
       </c>
       <c r="E118" s="2">
@@ -2589,7 +2589,7 @@
       <c r="C121" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="2">
         <v>3085</v>
       </c>
       <c r="E121" s="2">

--- a/metas.xlsx
+++ b/metas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/04 Abril/Liquidacióncvs - ensayo/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="864" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4003AA5-ABF3-4BE0-A9DF-AD5AF78E01DC}"/>
+  <xr:revisionPtr revIDLastSave="866" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D71A4081-4C97-480C-847E-4E46766B17EB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
